--- a/templates/Survey_Structure_Template.xlsx
+++ b/templates/Survey_Structure_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/templates/Final/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duncan/Documents/Turas/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6890F9CD-D30B-9246-9A8F-C4034CB1C389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E9F429-EF7F-D743-94A3-A105165E6FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23380" windowHeight="24000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24800" yWindow="1120" windowWidth="19600" windowHeight="23560" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -372,9 +372,6 @@
     <t>List of valid question types below</t>
   </si>
   <si>
-    <t>Single_Mention</t>
-  </si>
-  <si>
     <t>Multi_Mention</t>
   </si>
   <si>
@@ -1145,6 +1142,9 @@
   </si>
   <si>
     <t>Version 10.0 Last updated 4 December 2025</t>
+  </si>
+  <si>
+    <t>Single_Response</t>
   </si>
 </sst>
 </file>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -1858,7 +1858,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1899,7 +1899,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -2079,7 +2079,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2176,13 +2176,13 @@
         <v>42</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>60</v>
@@ -2191,10 +2191,10 @@
         <v>60</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="187" x14ac:dyDescent="0.2">
@@ -2211,7 +2211,7 @@
         <v>87</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>88</v>
@@ -2267,10 +2267,10 @@
         <v>38</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="34" x14ac:dyDescent="0.2">
@@ -2311,7 +2311,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -2327,10 +2327,10 @@
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -2366,7 +2366,7 @@
         <v>99</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -2384,7 +2384,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -2402,7 +2402,7 @@
         <v>24</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -2417,10 +2417,10 @@
     </row>
     <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -2456,7 +2456,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -2487,7 +2487,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2511,7 +2511,7 @@
         <v>26</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>73</v>
@@ -2523,16 +2523,16 @@
         <v>27</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>142</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -2597,16 +2597,16 @@
         <v>60</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>60</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="323" x14ac:dyDescent="0.2">
@@ -2614,31 +2614,31 @@
         <v>19</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>138</v>
-      </c>
       <c r="I7" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K7" s="17"/>
     </row>
@@ -2650,7 +2650,7 @@
         <v>74</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>38</v>
@@ -2659,13 +2659,13 @@
         <v>75</v>
       </c>
       <c r="F8" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="23" t="s">
         <v>128</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>129</v>
       </c>
       <c r="I8" s="23" t="s">
         <v>38</v>
@@ -2678,13 +2678,13 @@
         <v>76</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>130</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>131</v>
       </c>
       <c r="E9" s="17">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         <v>22</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>29</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -2747,18 +2747,18 @@
         <v>26</v>
       </c>
       <c r="C18" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>142</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="22">
         <v>18</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C20" s="22">
         <v>25</v>
@@ -2783,10 +2783,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="22">
         <v>35</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="22">
         <v>45</v>
@@ -2811,13 +2811,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B24" s="18"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" s="18"/>
     </row>
@@ -2842,7 +2842,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2932,7 +2932,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>60</v>
@@ -2949,28 +2949,28 @@
         <v>19</v>
       </c>
       <c r="B7" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="D7" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" s="21" t="s">
+      <c r="G7" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="H7" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="I7" s="21" t="s">
         <v>161</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="153" x14ac:dyDescent="0.2">
@@ -2978,22 +2978,22 @@
         <v>37</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>166</v>
-      </c>
       <c r="G8" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
@@ -3003,21 +3003,21 @@
         <v>76</v>
       </c>
       <c r="B9" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>167</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>168</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="17" t="s">
         <v>169</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>170</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I9" s="17"/>
     </row>
